--- a/lucas/import_data/utility/landscape/excel/land_use_family.xlsx
+++ b/lucas/import_data/utility/landscape/excel/land_use_family.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="71">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -34,6 +34,9 @@
     <t xml:space="preserve">display_name</t>
   </si>
   <si>
+    <t xml:space="preserve">tag</t>
+  </si>
+  <si>
     <t xml:space="preserve">agriculture</t>
   </si>
   <si>
@@ -64,6 +67,9 @@
     <t xml:space="preserve">Fishing and aquaculture</t>
   </si>
   <si>
+    <t xml:space="preserve">fishing</t>
+  </si>
+  <si>
     <t xml:space="preserve">mining and quarrying</t>
   </si>
   <si>
@@ -73,6 +79,9 @@
     <t xml:space="preserve">Mining and quarrying</t>
   </si>
   <si>
+    <t xml:space="preserve">mining</t>
+  </si>
+  <si>
     <t xml:space="preserve">other primary production</t>
   </si>
   <si>
@@ -82,6 +91,9 @@
     <t xml:space="preserve">Other primary production</t>
   </si>
   <si>
+    <t xml:space="preserve">primary-prod</t>
+  </si>
+  <si>
     <t xml:space="preserve">energy production</t>
   </si>
   <si>
@@ -94,6 +106,9 @@
     <t xml:space="preserve">Energy production</t>
   </si>
   <si>
+    <t xml:space="preserve">energy-prod</t>
+  </si>
+  <si>
     <t xml:space="preserve">industry and manufacturing</t>
   </si>
   <si>
@@ -103,6 +118,9 @@
     <t xml:space="preserve">Industry and manufacturing</t>
   </si>
   <si>
+    <t xml:space="preserve">industry</t>
+  </si>
+  <si>
     <t xml:space="preserve">transport infrastructure</t>
   </si>
   <si>
@@ -115,6 +133,9 @@
     <t xml:space="preserve">Transport infrastructure</t>
   </si>
   <si>
+    <t xml:space="preserve">transport</t>
+  </si>
+  <si>
     <t xml:space="preserve">water and waste treatment</t>
   </si>
   <si>
@@ -124,6 +145,9 @@
     <t xml:space="preserve">Water and Waste treatment</t>
   </si>
   <si>
+    <t xml:space="preserve">water-waste</t>
+  </si>
+  <si>
     <t xml:space="preserve">construction</t>
   </si>
   <si>
@@ -142,6 +166,9 @@
     <t xml:space="preserve">Commerical infrastructure</t>
   </si>
   <si>
+    <t xml:space="preserve">commerical</t>
+  </si>
+  <si>
     <t xml:space="preserve">community services</t>
   </si>
   <si>
@@ -151,6 +178,9 @@
     <t xml:space="preserve">Community services</t>
   </si>
   <si>
+    <t xml:space="preserve">community</t>
+  </si>
+  <si>
     <t xml:space="preserve">recreation</t>
   </si>
   <si>
@@ -178,6 +208,9 @@
     <t xml:space="preserve">Other infrastructure uses</t>
   </si>
   <si>
+    <t xml:space="preserve">other-infrastructure</t>
+  </si>
+  <si>
     <t xml:space="preserve">unused and abandoned land</t>
   </si>
   <si>
@@ -197,6 +230,9 @@
   </si>
   <si>
     <t xml:space="preserve">Semi-natural and natural areas not in use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">semi-/natural</t>
   </si>
 </sst>
 </file>
@@ -211,6 +247,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -270,8 +307,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -295,37 +336,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -398,265 +439,319 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="23.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="27.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>19</v>
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>23</v>
+      <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="0" t="s">
+      <c r="A8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>30</v>
+      <c r="A9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>33</v>
+      <c r="A10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="0" t="s">
+      <c r="A11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>36</v>
+      <c r="D11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>39</v>
+      <c r="A12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>42</v>
+      <c r="A13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>45</v>
+      <c r="A14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>48</v>
+      <c r="A15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="0" t="s">
-        <v>51</v>
+      <c r="A16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="0" t="s">
-        <v>55</v>
+      <c r="A17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>58</v>
+      <c r="A18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
